--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0419D957-8E52-4994-9CEB-FA1DF23810F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB8A244-D7FF-4E4C-885C-8A643FD082EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30855" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-12-2025" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 19-12-2025'!$A$1:$J$67</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 29-01-2026'!$A$1:$J$67</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB8A244-D7FF-4E4C-885C-8A643FD082EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C83DDF-9527-4190-89F0-931F261ACA33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 29-01-2026'!$A$1:$J$67</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 02-02-2026'!$A$1:$J$67</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C83DDF-9527-4190-89F0-931F261ACA33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFBE724D-FD05-4EE6-A1A7-61A1C7494994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 02-02-2026'!$A$1:$J$67</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 20-02-2026'!$A$1:$J$67</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -681,9 +681,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J67"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -715,7 +715,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -735,7 +735,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -752,7 +752,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -766,7 +766,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -786,7 +786,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -800,7 +800,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -814,7 +814,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -831,7 +831,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -848,7 +848,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -865,7 +865,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -879,7 +879,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -893,7 +893,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -910,7 +910,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -927,7 +927,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -944,7 +944,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -964,7 +964,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>42</v>
       </c>
@@ -981,7 +981,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -998,7 +998,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -1012,7 +1012,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1029,7 +1029,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1052,7 +1052,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1075,7 +1075,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1139,7 +1139,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>57</v>
       </c>
@@ -1171,7 +1171,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>59</v>
       </c>
@@ -1188,7 +1188,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>59</v>
       </c>
@@ -1202,7 +1202,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>62</v>
       </c>
@@ -1225,7 +1225,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>64</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>64</v>
       </c>
@@ -1259,7 +1259,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>67</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>67</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>67</v>
       </c>
@@ -1307,7 +1307,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>71</v>
       </c>
@@ -1327,7 +1327,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>73</v>
       </c>
@@ -1341,7 +1341,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>76</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>78</v>
       </c>
@@ -1407,7 +1407,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>80</v>
       </c>
@@ -1424,7 +1424,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>82</v>
       </c>
@@ -1438,7 +1438,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>82</v>
       </c>
@@ -1458,7 +1458,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>85</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>87</v>
       </c>
@@ -1492,7 +1492,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>10</v>
       </c>
@@ -1518,7 +1518,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>14</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>17</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>19</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>19</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>26</v>
       </c>
@@ -1600,7 +1600,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>28</v>
       </c>
@@ -1617,7 +1617,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>34</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>90</v>
       </c>
@@ -1651,7 +1651,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>90</v>
       </c>
@@ -1665,7 +1665,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>36</v>
       </c>
@@ -1682,7 +1682,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>49</v>
       </c>
@@ -1705,7 +1705,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>49</v>
       </c>
@@ -1719,7 +1719,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>51</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>55</v>
       </c>
@@ -1774,7 +1774,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>57</v>
       </c>
@@ -1806,7 +1806,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>59</v>
       </c>
@@ -1823,7 +1823,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>94</v>
       </c>
@@ -1840,7 +1840,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>96</v>
       </c>
@@ -1854,7 +1854,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>96</v>
       </c>
@@ -1874,7 +1874,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>99</v>
       </c>
@@ -1891,7 +1891,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>78</v>
       </c>
@@ -1923,7 +1923,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>101</v>
       </c>
@@ -1940,7 +1940,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>103</v>
       </c>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFBE724D-FD05-4EE6-A1A7-61A1C7494994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1770863E-E4DD-4ED2-89EE-1C727A746EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 20-02-2026'!$A$1:$J$67</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 04-03-2026'!$A$1:$J$67</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1770863E-E4DD-4ED2-89EE-1C727A746EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D64622-BCB9-4A19-B68F-1FBBAEB1C590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 04-03-2026'!$A$1:$J$67</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 06-03-2026'!$A$1:$J$67</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D64622-BCB9-4A19-B68F-1FBBAEB1C590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A69CEBD-FE11-4879-B919-D116CA0D88F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A69CEBD-FE11-4879-B919-D116CA0D88F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F29C42D3-8855-4F59-9D75-BCFF675EAB9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F29C42D3-8855-4F59-9D75-BCFF675EAB9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B97E339F-3F54-4DC6-BA79-C6ECA89D9543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 06-03-2026'!$A$1:$J$67</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 09-03-2026'!$A$1:$J$67</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B97E339F-3F54-4DC6-BA79-C6ECA89D9543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AEFD350-5A46-4678-BAA1-66283C0700D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AEFD350-5A46-4678-BAA1-66283C0700D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F7F26B6-229B-4A0E-B544-9C3652366F64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 09-03-2026'!$A$1:$J$67</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 11-03-2026'!$A$1:$J$67</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F7F26B6-229B-4A0E-B544-9C3652366F64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E69FAF-2B8C-4C49-B6AD-6C8B4F508D2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E69FAF-2B8C-4C49-B6AD-6C8B4F508D2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B5CC8A2-2609-4917-88E1-EF4651019759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 11-03-2026'!$A$1:$J$67</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 20-03-2026'!$A$1:$J$67</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B5CC8A2-2609-4917-88E1-EF4651019759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{939976B3-0562-4E0C-BC8B-A7B19E934902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 20-03-2026'!$A$1:$J$67</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 25-03-2026'!$A$1:$J$67</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{939976B3-0562-4E0C-BC8B-A7B19E934902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32FBA00C-7429-47DA-9EA5-85182427272E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 25-03-2026'!$A$1:$J$67</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 08-04-2026'!$A$1:$J$67</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32FBA00C-7429-47DA-9EA5-85182427272E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80B4359D-4D38-4603-B4B2-07373C7BA1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 08-04-2026'!$A$1:$J$67</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 10-04-2026'!$A$1:$J$67</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80B4359D-4D38-4603-B4B2-07373C7BA1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B50D524B-A88E-421E-8378-6028FC0A2F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B50D524B-A88E-421E-8378-6028FC0A2F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6FECA57-BDCE-4CF9-9550-6E6823D29A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 10-04-2026'!$A$1:$J$67</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 14-04-2026'!$A$1:$J$67</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6FECA57-BDCE-4CF9-9550-6E6823D29A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99335429-CAB9-41B9-A67E-4A0296273C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 14-04-2026'!$A$1:$J$67</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 24-04-2026'!$A$1:$J$67</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99335429-CAB9-41B9-A67E-4A0296273C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{693FB7E1-B041-4CF2-9EC8-EE6A7144C96B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{693FB7E1-B041-4CF2-9EC8-EE6A7144C96B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7828FF49-B922-4A8D-A887-EFCB1299B2BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 24-04-2026'!$A$1:$J$67</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 27-04-2026'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="104">
   <si>
     <t>Standard</t>
   </si>
@@ -85,11 +85,7 @@
     <t>CareCommunication</t>
   </si>
   <si>
-    <t>CareCommunication (4.0)</t>
-  </si>
-  <si>
-    <t>CareCommunication (5.0_x000D_
-5.0)</t>
+    <t>CareCommunication (5.0)</t>
   </si>
   <si>
     <t>Care Plan</t>
@@ -680,7 +676,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -779,6 +775,9 @@
       <c r="D5" t="s">
         <v>13</v>
       </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
       <c r="F5" t="s">
         <v>13</v>
       </c>
@@ -788,38 +787,41 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
       </c>
-      <c r="E6" t="s">
-        <v>13</v>
+      <c r="D6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
         <v>12</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
         <v>12</v>
@@ -833,10 +835,10 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
         <v>12</v>
@@ -850,72 +852,72 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
         <v>12</v>
       </c>
-      <c r="F10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="G10" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
       </c>
-      <c r="G11" t="s">
+      <c r="F11" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
         <v>12</v>
       </c>
       <c r="F12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
       </c>
-      <c r="F13" t="s">
-        <v>16</v>
-      </c>
-      <c r="I13" t="s">
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>
@@ -929,10 +931,10 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C15" t="s">
         <v>12</v>
@@ -941,15 +943,18 @@
         <v>16</v>
       </c>
       <c r="G15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
         <v>12</v>
@@ -958,15 +963,12 @@
         <v>16</v>
       </c>
       <c r="G16" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
         <v>43</v>
@@ -978,46 +980,46 @@
         <v>16</v>
       </c>
       <c r="G17" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
         <v>12</v>
       </c>
       <c r="D18" t="s">
         <v>16</v>
-      </c>
-      <c r="G18" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C19" t="s">
         <v>12</v>
       </c>
       <c r="D19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C20" t="s">
         <v>12</v>
@@ -1025,44 +1027,59 @@
       <c r="D20" t="s">
         <v>16</v>
       </c>
+      <c r="E20" t="s">
+        <v>16</v>
+      </c>
       <c r="G20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C21" t="s">
         <v>12</v>
       </c>
-      <c r="D21" t="s">
-        <v>16</v>
-      </c>
       <c r="E21" t="s">
         <v>16</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
         <v>16</v>
       </c>
       <c r="I21" t="s">
+        <v>16</v>
+      </c>
+      <c r="J21" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C22" t="s">
         <v>12</v>
       </c>
+      <c r="D22" t="s">
+        <v>16</v>
+      </c>
       <c r="E22" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" t="s">
         <v>16</v>
       </c>
       <c r="H22" t="s">
@@ -1077,10 +1094,10 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C23" t="s">
         <v>12</v>
@@ -1109,10 +1126,10 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C24" t="s">
         <v>12</v>
@@ -1141,30 +1158,15 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C25" t="s">
         <v>12</v>
       </c>
-      <c r="D25" t="s">
-        <v>16</v>
-      </c>
-      <c r="E25" t="s">
-        <v>16</v>
-      </c>
-      <c r="F25" t="s">
-        <v>16</v>
-      </c>
       <c r="G25" t="s">
-        <v>16</v>
-      </c>
-      <c r="H25" t="s">
-        <v>16</v>
-      </c>
-      <c r="I25" t="s">
         <v>16</v>
       </c>
       <c r="J25" t="s">
@@ -1173,7 +1175,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B26" t="s">
         <v>60</v>
@@ -1184,50 +1186,47 @@
       <c r="G26" t="s">
         <v>16</v>
       </c>
-      <c r="J26" t="s">
-        <v>16</v>
-      </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>
       </c>
+      <c r="D27" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" t="s">
+        <v>16</v>
+      </c>
       <c r="G27" t="s">
+        <v>16</v>
+      </c>
+      <c r="J27" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B28" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C28" t="s">
         <v>12</v>
       </c>
-      <c r="D28" t="s">
-        <v>16</v>
-      </c>
-      <c r="F28" t="s">
-        <v>16</v>
-      </c>
       <c r="G28" t="s">
-        <v>16</v>
-      </c>
-      <c r="J28" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B29" t="s">
         <v>65</v>
@@ -1235,33 +1234,33 @@
       <c r="C29" t="s">
         <v>12</v>
       </c>
+      <c r="D29" t="s">
+        <v>16</v>
+      </c>
       <c r="G29" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C30" t="s">
         <v>12</v>
       </c>
-      <c r="D30" t="s">
-        <v>16</v>
-      </c>
       <c r="G30" t="s">
-        <v>16</v>
-      </c>
-      <c r="J30" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B31" t="s">
         <v>68</v>
@@ -1275,7 +1274,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B32" t="s">
         <v>69</v>
@@ -1283,16 +1282,22 @@
       <c r="C32" t="s">
         <v>12</v>
       </c>
+      <c r="D32" t="s">
+        <v>16</v>
+      </c>
       <c r="G32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B33" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C33" t="s">
         <v>12</v>
@@ -1309,27 +1314,21 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C34" t="s">
         <v>12</v>
       </c>
-      <c r="D34" t="s">
-        <v>16</v>
-      </c>
       <c r="G34" t="s">
-        <v>16</v>
-      </c>
-      <c r="J34" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B35" t="s">
         <v>74</v>
@@ -1337,50 +1336,68 @@
       <c r="C35" t="s">
         <v>12</v>
       </c>
+      <c r="D35" t="s">
+        <v>16</v>
+      </c>
       <c r="G35" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B36" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C36" t="s">
         <v>12</v>
       </c>
-      <c r="D36" t="s">
-        <v>16</v>
-      </c>
       <c r="G36" t="s">
-        <v>16</v>
-      </c>
-      <c r="J36" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B37" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C37" t="s">
         <v>12</v>
       </c>
+      <c r="D37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" t="s">
+        <v>16</v>
+      </c>
+      <c r="F37" t="s">
+        <v>16</v>
+      </c>
       <c r="G37" t="s">
+        <v>16</v>
+      </c>
+      <c r="H37" t="s">
+        <v>16</v>
+      </c>
+      <c r="I37" t="s">
+        <v>16</v>
+      </c>
+      <c r="J37" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B38" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C38" t="s">
         <v>12</v>
@@ -1388,45 +1405,27 @@
       <c r="D38" t="s">
         <v>16</v>
       </c>
-      <c r="E38" t="s">
-        <v>16</v>
-      </c>
-      <c r="F38" t="s">
-        <v>16</v>
-      </c>
       <c r="G38" t="s">
-        <v>16</v>
-      </c>
-      <c r="H38" t="s">
-        <v>16</v>
-      </c>
-      <c r="I38" t="s">
-        <v>16</v>
-      </c>
-      <c r="J38" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B39" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C39" t="s">
         <v>12</v>
       </c>
       <c r="D39" t="s">
         <v>16</v>
-      </c>
-      <c r="G39" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B40" t="s">
         <v>83</v>
@@ -1437,13 +1436,19 @@
       <c r="D40" t="s">
         <v>16</v>
       </c>
+      <c r="G40" t="s">
+        <v>16</v>
+      </c>
+      <c r="J40" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B41" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C41" t="s">
         <v>12</v>
@@ -1452,18 +1457,15 @@
         <v>16</v>
       </c>
       <c r="G41" t="s">
-        <v>16</v>
-      </c>
-      <c r="J41" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B42" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C42" t="s">
         <v>12</v>
@@ -1477,121 +1479,127 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="B43" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="C43" t="s">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="D43" t="s">
         <v>16</v>
       </c>
+      <c r="E43" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43" t="s">
+        <v>13</v>
+      </c>
       <c r="G43" t="s">
+        <v>16</v>
+      </c>
+      <c r="J43" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B44" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C44" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D44" t="s">
         <v>16</v>
       </c>
-      <c r="E44" t="s">
-        <v>13</v>
-      </c>
-      <c r="F44" t="s">
-        <v>13</v>
-      </c>
       <c r="G44" t="s">
-        <v>16</v>
-      </c>
-      <c r="J44" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B45" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C45" t="s">
-        <v>89</v>
-      </c>
-      <c r="D45" t="s">
-        <v>16</v>
-      </c>
-      <c r="G45" t="s">
+        <v>88</v>
+      </c>
+      <c r="I45" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B46" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C46" t="s">
-        <v>89</v>
-      </c>
-      <c r="I46" t="s">
-        <v>16</v>
+        <v>88</v>
+      </c>
+      <c r="D46" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" t="s">
+        <v>13</v>
+      </c>
+      <c r="F46" t="s">
+        <v>13</v>
+      </c>
+      <c r="G46" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B47" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C47" t="s">
-        <v>89</v>
-      </c>
-      <c r="D47" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="F47" t="s">
-        <v>13</v>
-      </c>
-      <c r="G47" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="I47" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B48" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C48" t="s">
-        <v>89</v>
-      </c>
-      <c r="E48" t="s">
-        <v>13</v>
+        <v>88</v>
+      </c>
+      <c r="F48" t="s">
+        <v>16</v>
+      </c>
+      <c r="I48" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B49" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C49" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F49" t="s">
         <v>16</v>
@@ -1602,118 +1610,139 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="B50" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="C50" t="s">
-        <v>89</v>
-      </c>
-      <c r="F50" t="s">
-        <v>16</v>
-      </c>
-      <c r="I50" t="s">
+        <v>88</v>
+      </c>
+      <c r="D50" t="s">
+        <v>16</v>
+      </c>
+      <c r="J50" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="B51" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="C51" t="s">
-        <v>89</v>
-      </c>
-      <c r="F51" t="s">
-        <v>16</v>
-      </c>
-      <c r="I51" t="s">
+        <v>88</v>
+      </c>
+      <c r="D51" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="B52" t="s">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="C52" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D52" t="s">
         <v>16</v>
       </c>
-      <c r="J52" t="s">
+      <c r="G52" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="B53" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="C53" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D53" t="s">
+        <v>16</v>
+      </c>
+      <c r="E53" t="s">
+        <v>16</v>
+      </c>
+      <c r="G53" t="s">
+        <v>16</v>
+      </c>
+      <c r="I53" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B54" t="s">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="C54" t="s">
-        <v>89</v>
-      </c>
-      <c r="D54" t="s">
-        <v>16</v>
-      </c>
-      <c r="G54" t="s">
+        <v>88</v>
+      </c>
+      <c r="J54" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B55" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C55" t="s">
-        <v>89</v>
-      </c>
-      <c r="D55" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="E55" t="s">
         <v>16</v>
       </c>
-      <c r="G55" t="s">
+      <c r="H55" t="s">
         <v>16</v>
       </c>
       <c r="I55" t="s">
+        <v>16</v>
+      </c>
+      <c r="J55" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="C56" t="s">
-        <v>89</v>
+        <v>88</v>
+      </c>
+      <c r="D56" t="s">
+        <v>16</v>
+      </c>
+      <c r="E56" t="s">
+        <v>16</v>
+      </c>
+      <c r="F56" t="s">
+        <v>16</v>
+      </c>
+      <c r="G56" t="s">
+        <v>16</v>
+      </c>
+      <c r="H56" t="s">
+        <v>16</v>
+      </c>
+      <c r="I56" t="s">
+        <v>16</v>
       </c>
       <c r="J56" t="s">
         <v>16</v>
@@ -1721,15 +1750,24 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C57" t="s">
-        <v>89</v>
+        <v>88</v>
+      </c>
+      <c r="D57" t="s">
+        <v>16</v>
       </c>
       <c r="E57" t="s">
+        <v>16</v>
+      </c>
+      <c r="F57" t="s">
+        <v>16</v>
+      </c>
+      <c r="G57" t="s">
         <v>16</v>
       </c>
       <c r="H57" t="s">
@@ -1744,80 +1782,47 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B58" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C58" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D58" t="s">
         <v>16</v>
       </c>
-      <c r="E58" t="s">
-        <v>16</v>
-      </c>
-      <c r="F58" t="s">
-        <v>16</v>
-      </c>
       <c r="G58" t="s">
-        <v>16</v>
-      </c>
-      <c r="H58" t="s">
-        <v>16</v>
-      </c>
-      <c r="I58" t="s">
-        <v>16</v>
-      </c>
-      <c r="J58" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="B59" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="C59" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D59" t="s">
         <v>16</v>
       </c>
-      <c r="E59" t="s">
-        <v>16</v>
-      </c>
-      <c r="F59" t="s">
-        <v>16</v>
-      </c>
       <c r="G59" t="s">
-        <v>16</v>
-      </c>
-      <c r="H59" t="s">
-        <v>16</v>
-      </c>
-      <c r="I59" t="s">
-        <v>16</v>
-      </c>
-      <c r="J59" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="C60" t="s">
-        <v>89</v>
-      </c>
-      <c r="D60" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="G60" t="s">
         <v>16</v>
@@ -1825,30 +1830,36 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B61" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C61" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D61" t="s">
         <v>16</v>
       </c>
       <c r="G61" t="s">
+        <v>16</v>
+      </c>
+      <c r="J61" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B62" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C62" t="s">
-        <v>89</v>
+        <v>88</v>
+      </c>
+      <c r="D62" t="s">
+        <v>16</v>
       </c>
       <c r="G62" t="s">
         <v>16</v>
@@ -1856,18 +1867,30 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="B63" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="C63" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D63" t="s">
         <v>16</v>
       </c>
+      <c r="E63" t="s">
+        <v>16</v>
+      </c>
+      <c r="F63" t="s">
+        <v>16</v>
+      </c>
       <c r="G63" t="s">
+        <v>16</v>
+      </c>
+      <c r="H63" t="s">
+        <v>16</v>
+      </c>
+      <c r="I63" t="s">
         <v>16</v>
       </c>
       <c r="J63" t="s">
@@ -1876,81 +1899,32 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B64" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C64" t="s">
-        <v>89</v>
-      </c>
-      <c r="D64" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="G64" t="s">
+        <v>16</v>
+      </c>
+      <c r="J64" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="B65" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="C65" t="s">
-        <v>89</v>
-      </c>
-      <c r="D65" t="s">
-        <v>16</v>
-      </c>
-      <c r="E65" t="s">
-        <v>16</v>
-      </c>
-      <c r="F65" t="s">
-        <v>16</v>
-      </c>
-      <c r="G65" t="s">
-        <v>16</v>
-      </c>
-      <c r="H65" t="s">
-        <v>16</v>
-      </c>
-      <c r="I65" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="J65" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>101</v>
-      </c>
-      <c r="B66" t="s">
-        <v>102</v>
-      </c>
-      <c r="C66" t="s">
-        <v>89</v>
-      </c>
-      <c r="G66" t="s">
-        <v>16</v>
-      </c>
-      <c r="J66" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>103</v>
-      </c>
-      <c r="B67" t="s">
-        <v>104</v>
-      </c>
-      <c r="C67" t="s">
-        <v>89</v>
-      </c>
-      <c r="J67" t="s">
         <v>16</v>
       </c>
     </row>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7828FF49-B922-4A8D-A887-EFCB1299B2BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{710C413E-9330-41C9-94B5-7768F9AC62BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 27-04-2026'!$A$1:$J$65</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 06-05-2026'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{710C413E-9330-41C9-94B5-7768F9AC62BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B64E049-BFBE-480E-9C5A-E5CFD51047F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 06-05-2026'!$A$1:$J$65</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 01-06-2026'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B64E049-BFBE-480E-9C5A-E5CFD51047F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9722410-2529-4B6E-987D-7F9BDAFFE71D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 01-06-2026'!$A$1:$J$65</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 02-06-2026'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -49,7 +49,7 @@
     <t>NOVAX PPR (Novax)</t>
   </si>
   <si>
-    <t>OS2korrespondance (OS2)</t>
+    <t>OS2korrespondance (Digital Identity)</t>
   </si>
   <si>
     <t>Sensum Bosted _EOJ_ (EG)</t>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9722410-2529-4B6E-987D-7F9BDAFFE71D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E83E130-8542-4820-BE55-9B071DAFBF7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E83E130-8542-4820-BE55-9B071DAFBF7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29FD503F-0306-4054-8EED-CFD1B224C49A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 05-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 02-06-2026'!$A$1:$J$65</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 05-06-2026'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB8A244-D7FF-4E4C-885C-8A643FD082EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDEDBC9C-7CA7-401A-8A10-119E32E8B853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B4997F-0B5C-4D75-AF98-CEF0132F8017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17CE5AD0-B038-4484-ADEF-2EC2469346A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="3135" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17CE5AD0-B038-4484-ADEF-2EC2469346A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94B3BBFA-9A52-48CB-A8F8-E5706F5E6C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94B3BBFA-9A52-48CB-A8F8-E5706F5E6C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{741F66D1-3BE5-4B87-9C19-164CE98EA97A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 09-06-2026'!$A$1:$J$65</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 15-06-2026'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -677,9 +677,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -711,7 +711,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -731,7 +731,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -748,7 +748,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -762,7 +762,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -785,7 +785,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -799,7 +799,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -816,7 +816,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -833,7 +833,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -850,7 +850,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -864,7 +864,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>31</v>
       </c>
@@ -878,7 +878,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -895,7 +895,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -912,7 +912,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -929,7 +929,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>39</v>
       </c>
@@ -949,7 +949,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -966,7 +966,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -983,7 +983,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -997,7 +997,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>46</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>50</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>52</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>54</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>56</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1187,7 +1187,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>61</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>63</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>66</v>
       </c>
@@ -1258,7 +1258,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1272,7 +1272,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>70</v>
       </c>
@@ -1312,7 +1312,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>72</v>
       </c>
@@ -1326,7 +1326,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>77</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -1409,7 +1409,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -1423,7 +1423,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>84</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>86</v>
       </c>
@@ -1477,7 +1477,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>10</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>14</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>17</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>19</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>25</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>27</v>
       </c>
@@ -1591,7 +1591,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>33</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>89</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>89</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>35</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>48</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>48</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>50</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>56</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>58</v>
       </c>
@@ -1797,7 +1797,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>93</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>95</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>98</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>77</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>102</v>
       </c>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{741F66D1-3BE5-4B87-9C19-164CE98EA97A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE4A367D-830C-49D9-B950-702472E53952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 15-06-2026'!$A$1:$J$65</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 22-06-2026'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE4A367D-830C-49D9-B950-702472E53952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABEBA7F6-5C6C-44DE-B71A-BA700482F30E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 22-06-2026'!$A$1:$J$65</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 23-06-2026'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -677,9 +677,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J65"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -711,7 +711,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -731,7 +731,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -748,7 +748,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -762,7 +762,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -785,7 +785,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -799,7 +799,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -816,7 +816,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -833,7 +833,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -850,7 +850,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -864,7 +864,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>31</v>
       </c>
@@ -878,7 +878,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -895,7 +895,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -912,7 +912,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -929,7 +929,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>39</v>
       </c>
@@ -949,7 +949,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -966,7 +966,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -983,7 +983,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -997,7 +997,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>46</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>50</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>52</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>54</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>56</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1187,7 +1187,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>61</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>63</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>66</v>
       </c>
@@ -1258,7 +1258,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1272,7 +1272,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>70</v>
       </c>
@@ -1312,7 +1312,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>72</v>
       </c>
@@ -1326,7 +1326,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>77</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -1409,7 +1409,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -1423,7 +1423,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>84</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>86</v>
       </c>
@@ -1477,7 +1477,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>10</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>14</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>17</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>19</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>25</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>27</v>
       </c>
@@ -1591,7 +1591,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>33</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>89</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>89</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>35</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>48</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>48</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>50</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>56</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>58</v>
       </c>
@@ -1797,7 +1797,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>93</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>95</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>98</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>77</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>102</v>
       </c>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABEBA7F6-5C6C-44DE-B71A-BA700482F30E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D94E7595-1E37-46EA-A8D3-55848CFD7561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE4A367D-830C-49D9-B950-702472E53952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB3281C2-FDFC-4E7D-A071-E7F855FC40BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 22-06-2026'!$A$1:$J$65</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 23-06-2026'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB3281C2-FDFC-4E7D-A071-E7F855FC40BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E15908F-F788-483B-A756-FC3C3C6232C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 23-06-2026'!$A$1:$J$65</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 25-06-2026'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E15908F-F788-483B-A756-FC3C3C6232C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD7D58D0-3A27-48F8-9B34-22392CE31BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 25-06-2026'!$A$1:$J$65</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 30-06-2026'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD7D58D0-3A27-48F8-9B34-22392CE31BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA234EED-D87D-47BB-A6F1-1F328565FBB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA234EED-D87D-47BB-A6F1-1F328565FBB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F145C68D-7D41-43A3-BF1C-501B99AB9B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 30-06-2026'!$A$1:$J$65</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 01-07-2026'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -64,6 +64,9 @@
     <t>Modtage</t>
   </si>
   <si>
+    <t>Godkendt</t>
+  </si>
+  <si>
     <t>Tester</t>
   </si>
   <si>
@@ -71,9 +74,6 @@
   </si>
   <si>
     <t>APD-DK (2.0.1)</t>
-  </si>
-  <si>
-    <t>Godkendt</t>
   </si>
   <si>
     <t>Binær dokumenttransport</t>
@@ -677,9 +677,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J65"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -711,7 +711,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -725,30 +725,30 @@
         <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
         <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -759,10 +759,10 @@
         <v>12</v>
       </c>
       <c r="I4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -776,16 +776,16 @@
         <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -796,10 +796,10 @@
         <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -810,13 +810,13 @@
         <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -827,13 +827,13 @@
         <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -844,13 +844,13 @@
         <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -861,10 +861,10 @@
         <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>31</v>
       </c>
@@ -875,10 +875,10 @@
         <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -889,13 +889,13 @@
         <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -906,13 +906,13 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -923,13 +923,13 @@
         <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>39</v>
       </c>
@@ -940,16 +940,16 @@
         <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G15" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -960,13 +960,13 @@
         <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -977,13 +977,13 @@
         <v>12</v>
       </c>
       <c r="D17" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G17" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -994,10 +994,10 @@
         <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>46</v>
       </c>
@@ -1008,13 +1008,13 @@
         <v>12</v>
       </c>
       <c r="D19" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G19" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -1025,19 +1025,19 @@
         <v>12</v>
       </c>
       <c r="D20" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E20" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G20" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I20" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>50</v>
       </c>
@@ -1048,19 +1048,19 @@
         <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H21" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I21" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J21" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>52</v>
       </c>
@@ -1071,28 +1071,28 @@
         <v>12</v>
       </c>
       <c r="D22" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E22" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F22" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G22" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H22" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I22" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J22" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>54</v>
       </c>
@@ -1103,28 +1103,28 @@
         <v>12</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E23" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F23" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G23" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H23" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I23" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J23" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>56</v>
       </c>
@@ -1135,28 +1135,28 @@
         <v>12</v>
       </c>
       <c r="D24" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E24" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F24" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G24" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H24" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I24" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -1167,13 +1167,13 @@
         <v>12</v>
       </c>
       <c r="G25" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J25" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1184,10 +1184,10 @@
         <v>12</v>
       </c>
       <c r="G26" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>61</v>
       </c>
@@ -1198,19 +1198,19 @@
         <v>12</v>
       </c>
       <c r="D27" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F27" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G27" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J27" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>63</v>
       </c>
@@ -1221,10 +1221,10 @@
         <v>12</v>
       </c>
       <c r="G28" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1235,16 +1235,16 @@
         <v>12</v>
       </c>
       <c r="D29" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G29" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>66</v>
       </c>
@@ -1255,10 +1255,10 @@
         <v>12</v>
       </c>
       <c r="G30" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1269,10 +1269,10 @@
         <v>12</v>
       </c>
       <c r="G31" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1283,16 +1283,16 @@
         <v>12</v>
       </c>
       <c r="D32" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G32" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J32" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>70</v>
       </c>
@@ -1303,16 +1303,16 @@
         <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G33" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J33" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>72</v>
       </c>
@@ -1323,10 +1323,10 @@
         <v>12</v>
       </c>
       <c r="G34" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -1337,16 +1337,16 @@
         <v>12</v>
       </c>
       <c r="D35" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G35" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J35" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1357,10 +1357,10 @@
         <v>12</v>
       </c>
       <c r="G36" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>77</v>
       </c>
@@ -1371,28 +1371,28 @@
         <v>12</v>
       </c>
       <c r="D37" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E37" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F37" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G37" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H37" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I37" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J37" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -1403,13 +1403,13 @@
         <v>12</v>
       </c>
       <c r="D38" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G38" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -1420,10 +1420,10 @@
         <v>12</v>
       </c>
       <c r="D39" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -1434,16 +1434,16 @@
         <v>12</v>
       </c>
       <c r="D40" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G40" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J40" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>84</v>
       </c>
@@ -1454,13 +1454,13 @@
         <v>12</v>
       </c>
       <c r="D41" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G41" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>86</v>
       </c>
@@ -1471,13 +1471,13 @@
         <v>12</v>
       </c>
       <c r="D42" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G42" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>10</v>
       </c>
@@ -1488,39 +1488,39 @@
         <v>88</v>
       </c>
       <c r="D43" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" t="s">
+        <v>14</v>
+      </c>
+      <c r="F43" t="s">
+        <v>14</v>
+      </c>
+      <c r="G43" t="s">
+        <v>13</v>
+      </c>
+      <c r="J43" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
         <v>16</v>
       </c>
-      <c r="E43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F43" t="s">
-        <v>13</v>
-      </c>
-      <c r="G43" t="s">
-        <v>16</v>
-      </c>
-      <c r="J43" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>14</v>
-      </c>
-      <c r="B44" t="s">
-        <v>15</v>
-      </c>
       <c r="C44" t="s">
         <v>88</v>
       </c>
       <c r="D44" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G44" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>17</v>
       </c>
@@ -1531,10 +1531,10 @@
         <v>88</v>
       </c>
       <c r="I45" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>19</v>
       </c>
@@ -1548,16 +1548,16 @@
         <v>13</v>
       </c>
       <c r="E46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G46" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>25</v>
       </c>
@@ -1568,13 +1568,13 @@
         <v>88</v>
       </c>
       <c r="F47" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I47" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>27</v>
       </c>
@@ -1585,13 +1585,13 @@
         <v>88</v>
       </c>
       <c r="F48" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I48" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>33</v>
       </c>
@@ -1602,13 +1602,13 @@
         <v>88</v>
       </c>
       <c r="F49" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I49" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>89</v>
       </c>
@@ -1619,13 +1619,13 @@
         <v>88</v>
       </c>
       <c r="D50" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J50" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>89</v>
       </c>
@@ -1636,10 +1636,10 @@
         <v>88</v>
       </c>
       <c r="D51" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>35</v>
       </c>
@@ -1650,13 +1650,13 @@
         <v>88</v>
       </c>
       <c r="D52" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G52" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>48</v>
       </c>
@@ -1667,19 +1667,19 @@
         <v>88</v>
       </c>
       <c r="D53" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E53" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G53" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I53" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>48</v>
       </c>
@@ -1690,10 +1690,10 @@
         <v>88</v>
       </c>
       <c r="J54" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>50</v>
       </c>
@@ -1704,19 +1704,19 @@
         <v>88</v>
       </c>
       <c r="E55" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H55" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I55" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J55" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -1727,28 +1727,28 @@
         <v>88</v>
       </c>
       <c r="D56" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E56" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F56" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G56" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H56" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I56" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J56" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>56</v>
       </c>
@@ -1759,28 +1759,28 @@
         <v>88</v>
       </c>
       <c r="D57" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E57" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F57" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G57" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H57" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I57" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J57" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>58</v>
       </c>
@@ -1791,13 +1791,13 @@
         <v>88</v>
       </c>
       <c r="D58" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G58" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>93</v>
       </c>
@@ -1808,13 +1808,13 @@
         <v>88</v>
       </c>
       <c r="D59" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G59" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -1825,10 +1825,10 @@
         <v>88</v>
       </c>
       <c r="G60" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>95</v>
       </c>
@@ -1839,16 +1839,16 @@
         <v>88</v>
       </c>
       <c r="D61" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G61" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J61" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>98</v>
       </c>
@@ -1859,13 +1859,13 @@
         <v>88</v>
       </c>
       <c r="D62" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G62" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>77</v>
       </c>
@@ -1876,28 +1876,28 @@
         <v>88</v>
       </c>
       <c r="D63" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E63" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F63" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G63" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H63" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I63" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J63" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -1908,13 +1908,13 @@
         <v>88</v>
       </c>
       <c r="G64" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J64" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>102</v>
       </c>
@@ -1925,7 +1925,7 @@
         <v>88</v>
       </c>
       <c r="J65" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F145C68D-7D41-43A3-BF1C-501B99AB9B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E7BDB1-F55C-4AFD-A06F-3936E79B459C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 01-07-2026'!$A$1:$J$65</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 02-07-2026'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F145C68D-7D41-43A3-BF1C-501B99AB9B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8B25BFF-E8DD-45A7-90F4-8B02E74039A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 01-07-2026'!$A$1:$J$65</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 03-07-2026'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -677,9 +677,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -711,7 +711,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -731,7 +731,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -748,7 +748,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -762,7 +762,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -785,7 +785,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -799,7 +799,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -816,7 +816,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -833,7 +833,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -850,7 +850,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -864,7 +864,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>31</v>
       </c>
@@ -878,7 +878,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -895,7 +895,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -912,7 +912,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -929,7 +929,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>39</v>
       </c>
@@ -949,7 +949,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -966,7 +966,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -983,7 +983,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -997,7 +997,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>46</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>50</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>52</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>54</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>56</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1187,7 +1187,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>61</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>63</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>66</v>
       </c>
@@ -1258,7 +1258,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1272,7 +1272,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>70</v>
       </c>
@@ -1312,7 +1312,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>72</v>
       </c>
@@ -1326,7 +1326,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>77</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -1409,7 +1409,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -1423,7 +1423,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>84</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>86</v>
       </c>
@@ -1477,7 +1477,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>10</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>15</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>17</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>19</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>25</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>27</v>
       </c>
@@ -1591,7 +1591,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>33</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>89</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>89</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>35</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>48</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>48</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>50</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>56</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>58</v>
       </c>
@@ -1797,7 +1797,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>93</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>95</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>98</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>77</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>102</v>
       </c>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E7BDB1-F55C-4AFD-A06F-3936E79B459C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C430FD35-D69E-4CED-A390-D750560C0066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 02-07-2026'!$A$1:$J$65</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 03-07-2026'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -677,9 +677,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -711,7 +711,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -731,7 +731,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -748,7 +748,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -762,7 +762,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -785,7 +785,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -799,7 +799,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -816,7 +816,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -833,7 +833,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -850,7 +850,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -864,7 +864,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>31</v>
       </c>
@@ -878,7 +878,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -895,7 +895,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -912,7 +912,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -929,7 +929,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>39</v>
       </c>
@@ -949,7 +949,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -966,7 +966,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -983,7 +983,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -997,7 +997,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>46</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>50</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>52</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>54</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>56</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1187,7 +1187,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>61</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>63</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>66</v>
       </c>
@@ -1258,7 +1258,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1272,7 +1272,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>70</v>
       </c>
@@ -1312,7 +1312,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>72</v>
       </c>
@@ -1326,7 +1326,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>77</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -1409,7 +1409,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -1423,7 +1423,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>84</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>86</v>
       </c>
@@ -1477,7 +1477,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>10</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>15</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>17</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>19</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>25</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>27</v>
       </c>
@@ -1591,7 +1591,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>33</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>89</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>89</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>35</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>48</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>48</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>50</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>56</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>58</v>
       </c>
@@ -1797,7 +1797,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>93</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>95</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>98</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>77</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>102</v>
       </c>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C430FD35-D69E-4CED-A390-D750560C0066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F11BE512-7717-45BF-972A-B262FEF14A0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 03-07-2026'!$A$1:$J$65</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 09-07-2026'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -728,7 +728,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -779,7 +779,7 @@
         <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G5" t="s">
         <v>14</v>
@@ -1494,7 +1494,7 @@
         <v>14</v>
       </c>
       <c r="F43" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G43" t="s">
         <v>13</v>
@@ -1551,7 +1551,7 @@
         <v>14</v>
       </c>
       <c r="F46" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G46" t="s">
         <v>14</v>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F11BE512-7717-45BF-972A-B262FEF14A0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4804DDF3-F017-4682-B7A0-EBFDF903B139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 09-07-2026'!$A$1:$J$65</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 19-08-2026'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4804DDF3-F017-4682-B7A0-EBFDF903B139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D909F5E9-1BF7-43C9-94FA-869A2896B75A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 19-08-2026'!$A$1:$J$65</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 21-08-2026'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -677,9 +677,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J65"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -711,7 +711,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -731,7 +731,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -748,7 +748,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -762,7 +762,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -785,7 +785,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -799,7 +799,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -816,7 +816,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -833,7 +833,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -850,7 +850,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -864,7 +864,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>31</v>
       </c>
@@ -878,7 +878,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -895,7 +895,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -912,7 +912,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -929,7 +929,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>39</v>
       </c>
@@ -949,7 +949,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -966,7 +966,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -983,7 +983,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -997,7 +997,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>46</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>50</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>52</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>54</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>56</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1187,7 +1187,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>61</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>63</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>66</v>
       </c>
@@ -1258,7 +1258,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1272,7 +1272,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>70</v>
       </c>
@@ -1312,7 +1312,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>72</v>
       </c>
@@ -1326,7 +1326,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>77</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -1409,7 +1409,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -1423,7 +1423,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>84</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>86</v>
       </c>
@@ -1477,7 +1477,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>10</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>15</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>17</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>19</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>25</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>27</v>
       </c>
@@ -1591,7 +1591,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>33</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>89</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>89</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>35</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>48</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>48</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>50</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>56</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>58</v>
       </c>
@@ -1797,7 +1797,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>93</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>95</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>98</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>77</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>102</v>
       </c>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D909F5E9-1BF7-43C9-94FA-869A2896B75A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D91E839-BC35-43BF-876C-411735863A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 21-08-2026'!$A$1:$J$65</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 27-08-2026'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -677,9 +677,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -711,7 +711,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -731,7 +731,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -748,7 +748,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -762,7 +762,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -785,7 +785,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -799,7 +799,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -816,7 +816,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -833,7 +833,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -850,7 +850,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -864,7 +864,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>31</v>
       </c>
@@ -878,7 +878,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -895,7 +895,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -912,7 +912,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -929,7 +929,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>39</v>
       </c>
@@ -949,7 +949,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -966,7 +966,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -983,7 +983,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -997,7 +997,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>46</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>50</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>52</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>54</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>56</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1187,7 +1187,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>61</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>63</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>66</v>
       </c>
@@ -1258,7 +1258,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1272,7 +1272,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>70</v>
       </c>
@@ -1312,7 +1312,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>72</v>
       </c>
@@ -1326,7 +1326,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>77</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -1409,7 +1409,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -1423,7 +1423,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>84</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>86</v>
       </c>
@@ -1477,7 +1477,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>10</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>15</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>17</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>19</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>25</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>27</v>
       </c>
@@ -1591,7 +1591,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>33</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>89</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>89</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>35</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>48</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>48</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>50</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>56</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>58</v>
       </c>
@@ -1797,7 +1797,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>93</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>95</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>98</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>77</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>102</v>
       </c>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D91E839-BC35-43BF-876C-411735863A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6510A3DF-3733-4CEE-AF2C-6A2E71239078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 27-08-2026'!$A$1:$J$65</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 02-09-2026'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6510A3DF-3733-4CEE-AF2C-6A2E71239078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF34EAEC-46B4-42D8-94D7-05F72E4B2640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 02-09-2026'!$A$1:$J$65</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 06-09-2026'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF34EAEC-46B4-42D8-94D7-05F72E4B2640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45DC0682-D8FF-4950-B4F5-2FE83027B751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45DC0682-D8FF-4950-B4F5-2FE83027B751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B7F2F2-35D2-4AE3-BB5A-4E3F88A0B00D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 06-09-2026'!$A$1:$J$65</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 07-09-2026'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B7F2F2-35D2-4AE3-BB5A-4E3F88A0B00D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E32C9B99-BC99-4545-A948-3DFC871C0576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PPR_systemer">'Opdateret d. 07-09-2026'!$A$1:$J$65</definedName>
+    <definedName name="PPR_systemer">'Opdateret d. 09-09-2026'!$A$1:$J$65</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PPR-systemer_excel.XLSX
+++ b/html/PPR-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E32C9B99-BC99-4545-A948-3DFC871C0576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A08E9334-D472-4AFA-A6A3-429F203CA542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
